--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 이벤트 데이터 테이블 V1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 이벤트 데이터 테이블 V1.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200039\Desktop\작업\. 문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4CFD28-FFD8-4B9E-BEF1-6203DBE28260}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B010DBEC-665E-4C4D-86E5-D530AE9BF80E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17130" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문서 개요" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="486">
   <si>
     <t>《Hero Influence》 이벤트 데이터 테이블</t>
   </si>
@@ -1549,10 +1549,6 @@
   </si>
   <si>
     <t>Choice_Condition_001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>=</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2443,18 +2439,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2468,7 +2452,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2480,6 +2470,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2970,13 +2966,13 @@
         <v>46268</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F8" s="5"/>
     </row>
@@ -3250,13 +3246,13 @@
     </row>
     <row r="5" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="46" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>471</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D5" s="18">
         <v>0</v>
@@ -3277,22 +3273,22 @@
         <v>40</v>
       </c>
       <c r="L5" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="M5" s="46" t="s">
         <v>477</v>
-      </c>
-      <c r="M5" s="46" t="s">
-        <v>478</v>
       </c>
       <c r="N5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="46" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>471</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D6" s="18">
         <v>5</v>
@@ -3319,10 +3315,10 @@
         <v>25</v>
       </c>
       <c r="L6" s="46" t="s">
+        <v>480</v>
+      </c>
+      <c r="M6" s="46" t="s">
         <v>481</v>
-      </c>
-      <c r="M6" s="46" t="s">
-        <v>482</v>
       </c>
       <c r="N6" s="30"/>
     </row>
@@ -3637,7 +3633,7 @@
         <v>114</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C1" s="23" t="s">
         <v>116</v>
@@ -3749,12 +3745,12 @@
         <v>-10</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="46" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B7" s="20">
         <v>1</v>
@@ -3772,7 +3768,7 @@
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="46" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B8" s="20">
         <v>1</v>
@@ -3790,7 +3786,7 @@
     </row>
     <row r="9" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B9" s="20">
         <v>1</v>
@@ -3808,7 +3804,7 @@
     </row>
     <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B10" s="20">
         <v>1</v>
@@ -6083,16 +6079,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="58"/>
@@ -6105,16 +6101,16 @@
       <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="107" t="s">
         <v>261</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="101"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
@@ -6309,16 +6305,16 @@
       <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="95" t="s">
         <v>288</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="97"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="65" t="s">
@@ -6513,16 +6509,16 @@
       <c r="H20" s="72"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="102" t="s">
+      <c r="A21" s="98" t="s">
         <v>320</v>
       </c>
-      <c r="B21" s="97"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="101"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="73" t="s">
@@ -6691,16 +6687,16 @@
       <c r="H28" s="72"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="99" t="s">
+      <c r="A29" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="B29" s="100"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="101"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="97"/>
     </row>
     <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="65" t="s">
@@ -6999,16 +6995,16 @@
       <c r="H41" s="72"/>
     </row>
     <row r="42" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="99" t="s">
+      <c r="A42" s="95" t="s">
         <v>356</v>
       </c>
-      <c r="B42" s="100"/>
-      <c r="C42" s="100"/>
-      <c r="D42" s="100"/>
-      <c r="E42" s="100"/>
-      <c r="F42" s="100"/>
-      <c r="G42" s="100"/>
-      <c r="H42" s="101"/>
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
+      <c r="H42" s="97"/>
     </row>
     <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="65" t="s">
@@ -7177,16 +7173,16 @@
       <c r="H49" s="80"/>
     </row>
     <row r="50" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="102" t="s">
+      <c r="A50" s="98" t="s">
         <v>370</v>
       </c>
-      <c r="B50" s="97"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="103"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="97"/>
-      <c r="G50" s="97"/>
-      <c r="H50" s="98"/>
+      <c r="B50" s="99"/>
+      <c r="C50" s="100"/>
+      <c r="D50" s="100"/>
+      <c r="E50" s="100"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="101"/>
     </row>
     <row r="51" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="65" t="s">
@@ -7277,16 +7273,16 @@
       <c r="H54" s="84"/>
     </row>
     <row r="55" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="104" t="s">
+      <c r="A55" s="102" t="s">
         <v>376</v>
       </c>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="106"/>
-      <c r="G55" s="106"/>
-      <c r="H55" s="107"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="103"/>
+      <c r="D55" s="103"/>
+      <c r="E55" s="103"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="105"/>
     </row>
     <row r="56" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="65" t="s">
@@ -7663,16 +7659,16 @@
       <c r="H70" s="84"/>
     </row>
     <row r="71" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="104" t="s">
+      <c r="A71" s="102" t="s">
         <v>412</v>
       </c>
-      <c r="B71" s="105"/>
-      <c r="C71" s="105"/>
-      <c r="D71" s="105"/>
-      <c r="E71" s="105"/>
-      <c r="F71" s="106"/>
-      <c r="G71" s="106"/>
-      <c r="H71" s="107"/>
+      <c r="B71" s="103"/>
+      <c r="C71" s="103"/>
+      <c r="D71" s="103"/>
+      <c r="E71" s="103"/>
+      <c r="F71" s="104"/>
+      <c r="G71" s="104"/>
+      <c r="H71" s="105"/>
     </row>
     <row r="72" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="65" t="s">
@@ -11395,20 +11391,20 @@
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="18" t="s">
-        <v>472</v>
+      <c r="G3" s="18">
+        <v>2</v>
       </c>
       <c r="H3" s="18">
         <v>12</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J3" s="20">
         <v>4</v>
       </c>
       <c r="K3" s="20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
@@ -11733,5 +11729,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>